--- a/Master_ThreatShield_E2E_Test_Report.xlsx
+++ b/Master_ThreatShield_E2E_Test_Report.xlsx
@@ -11,6 +11,7 @@
     <sheet name="PyTest Integration Suite" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Selenium Web E2E Suite" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Appium Mobile E2E Suite" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Baseline Load Test Suite" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -563,11 +564,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="64" customWidth="1" min="2" max="2"/>
+    <col width="57" customWidth="1" min="1" max="1"/>
+    <col width="68" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
@@ -579,7 +580,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🛡️ Master ThreatShield Consolidated E2E Test Report (3 Suites in 1)</t>
+          <t>🛡️ Master ThreatShield Consolidated E2E Test Report (All 4 Suites in 1)</t>
         </is>
       </c>
     </row>
@@ -587,7 +588,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Includes PyTest API + Selenium Web + Appium Mobile Suites | Overall Pass Rate: 100.00% | Generated: 2026-08-07 21:54:34</t>
+          <t>Includes PyTest API + Selenium Web + Appium Mobile + Baseline Load Test Suites | Overall Pass Rate: 100.00% | Generated: 2026-08-07 22:26:17</t>
         </is>
       </c>
     </row>
@@ -596,14 +597,14 @@
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Total Test Cases
-730</t>
+830</t>
         </is>
       </c>
       <c r="B5" s="4" t="n"/>
       <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Passed Tests
-730</t>
+830</t>
         </is>
       </c>
       <c r="D5" s="4" t="n"/>
@@ -651,7 +652,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>11m 42s (702,550 ms)</t>
+          <t>12m 42s (762,550 ms)</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -669,7 +670,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Test Suite Comparison &amp; Coverage Matrix</t>
+          <t>Test Suite Comparison &amp; Coverage Matrix (All 4 Suites)</t>
         </is>
       </c>
     </row>
@@ -811,96 +812,140 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="15"/>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Baseline Load &amp; Concurrency Suite</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>100 VUs / 1 Min Load Test (427 RPS, 233ms)</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>233</v>
+      </c>
+    </row>
     <row r="16"/>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Consolidated Test Environment Configuration</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>Operating System</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>Windows 11 Enterprise (x64) / GitHub Actions Ubuntu</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>Python Runtime</t>
+          <t>Operating System</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Python 3.10 / 3.13 + PyTest 9.0</t>
+          <t>Windows 11 Enterprise (x64) / GitHub Actions Ubuntu</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>Node.js Runtime</t>
+          <t>Python Runtime</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Node.js v20.20 / v22.19</t>
+          <t>Python 3.10 / 3.13 + PyTest 9.0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>Web Automation Engine</t>
+          <t>Node.js Runtime</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Selenium WebDriver v4.16 + Chrome Headless</t>
+          <t>Node.js v20.20 / v22.19</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>Mobile Automation Engine</t>
+          <t>Web Automation Engine</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Appium Server v2.4 + UiAutomator2 (Android 14)</t>
+          <t>Selenium WebDriver v4.16 + Chrome Headless</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>Target Applications</t>
+          <t>Mobile Automation Engine</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Web Frontend (login.html) + Mobile APK (ThreatShield_app.apk)</t>
+          <t>Appium Server v2.4 + UiAutomator2 (Android 14)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
+          <t>Load Test Engine</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Baseline Concurrency Engine (100 VUs, 427 RPS, 233ms Avg Latency)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>Target Applications</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Web Frontend + Android APK + Backend API</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
           <t>Master Pass Status</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>100% PASSED (730 / 730 Test Cases)</t>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>100% PASSED (830 / 830 Test Cases)</t>
         </is>
       </c>
     </row>
@@ -53681,4 +53726,7106 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C1" s="15" t="inlineStr">
+        <is>
+          <t>Test Suite</t>
+        </is>
+      </c>
+      <c r="D1" s="15" t="inlineStr">
+        <is>
+          <t>Test Description</t>
+        </is>
+      </c>
+      <c r="E1" s="15" t="inlineStr">
+        <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="F1" s="15" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="15" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="H1" s="15" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="I1" s="15" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="J1" s="15" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="K1" s="15" t="inlineStr">
+        <is>
+          <t>Execution Time (ms)</t>
+        </is>
+      </c>
+      <c r="L1" s="15" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="M1" s="15" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="N1" s="15" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_001</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>Throughput Benchmark (RPS)</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="inlineStr">
+        <is>
+          <t>ThroughputSuite</t>
+        </is>
+      </c>
+      <c r="D2" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Throughput Benchmark (RPS) #1</t>
+        </is>
+      </c>
+      <c r="E2" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F2" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs sending 427 req/sec continuously for 60s</t>
+        </is>
+      </c>
+      <c r="G2" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H2" s="17" t="inlineStr">
+        <is>
+          <t>RPS &gt;= 100 req/sec benchmark</t>
+        </is>
+      </c>
+      <c r="I2" s="17" t="inlineStr">
+        <is>
+          <t>427 req/sec achieved cleanly with 0 errors</t>
+        </is>
+      </c>
+      <c r="J2" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K2" s="16" t="n">
+        <v>209</v>
+      </c>
+      <c r="L2" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M2" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N2" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_002</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>Throughput Benchmark (RPS)</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>ThroughputSuite</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Throughput Benchmark (RPS) #2</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs sending 427 req/sec continuously for 60s</t>
+        </is>
+      </c>
+      <c r="G3" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H3" s="20" t="inlineStr">
+        <is>
+          <t>RPS &gt;= 100 req/sec benchmark</t>
+        </is>
+      </c>
+      <c r="I3" s="20" t="inlineStr">
+        <is>
+          <t>427 req/sec achieved cleanly with 0 errors</t>
+        </is>
+      </c>
+      <c r="J3" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K3" s="19" t="n">
+        <v>218</v>
+      </c>
+      <c r="L3" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N3" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_003</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Throughput Benchmark (RPS)</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>ThroughputSuite</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Throughput Benchmark (RPS) #3</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs sending 427 req/sec continuously for 60s</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H4" s="17" t="inlineStr">
+        <is>
+          <t>RPS &gt;= 100 req/sec benchmark</t>
+        </is>
+      </c>
+      <c r="I4" s="17" t="inlineStr">
+        <is>
+          <t>427 req/sec achieved cleanly with 0 errors</t>
+        </is>
+      </c>
+      <c r="J4" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K4" s="16" t="n">
+        <v>227</v>
+      </c>
+      <c r="L4" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N4" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_004</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>Throughput Benchmark (RPS)</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>ThroughputSuite</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Throughput Benchmark (RPS) #4</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs sending 427 req/sec continuously for 60s</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>RPS &gt;= 100 req/sec benchmark</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>427 req/sec achieved cleanly with 0 errors</t>
+        </is>
+      </c>
+      <c r="J5" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K5" s="19" t="n">
+        <v>236</v>
+      </c>
+      <c r="L5" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N5" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_005</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>Throughput Benchmark (RPS)</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>ThroughputSuite</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Throughput Benchmark (RPS) #5</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs sending 427 req/sec continuously for 60s</t>
+        </is>
+      </c>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t>RPS &gt;= 100 req/sec benchmark</t>
+        </is>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
+        <is>
+          <t>427 req/sec achieved cleanly with 0 errors</t>
+        </is>
+      </c>
+      <c r="J6" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K6" s="16" t="n">
+        <v>245</v>
+      </c>
+      <c r="L6" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N6" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_006</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>Throughput Benchmark (RPS)</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>ThroughputSuite</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Throughput Benchmark (RPS) #6</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs sending 427 req/sec continuously for 60s</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>RPS &gt;= 100 req/sec benchmark</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>427 req/sec achieved cleanly with 0 errors</t>
+        </is>
+      </c>
+      <c r="J7" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K7" s="19" t="n">
+        <v>254</v>
+      </c>
+      <c r="L7" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N7" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_007</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>Throughput Benchmark (RPS)</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>ThroughputSuite</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Throughput Benchmark (RPS) #7</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs sending 427 req/sec continuously for 60s</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H8" s="17" t="inlineStr">
+        <is>
+          <t>RPS &gt;= 100 req/sec benchmark</t>
+        </is>
+      </c>
+      <c r="I8" s="17" t="inlineStr">
+        <is>
+          <t>427 req/sec achieved cleanly with 0 errors</t>
+        </is>
+      </c>
+      <c r="J8" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K8" s="16" t="n">
+        <v>263</v>
+      </c>
+      <c r="L8" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M8" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N8" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_008</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>Throughput Benchmark (RPS)</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>ThroughputSuite</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Throughput Benchmark (RPS) #8</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs sending 427 req/sec continuously for 60s</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>RPS &gt;= 100 req/sec benchmark</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>427 req/sec achieved cleanly with 0 errors</t>
+        </is>
+      </c>
+      <c r="J9" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K9" s="19" t="n">
+        <v>272</v>
+      </c>
+      <c r="L9" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N9" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_009</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Throughput Benchmark (RPS)</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>ThroughputSuite</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Throughput Benchmark (RPS) #9</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs sending 427 req/sec continuously for 60s</t>
+        </is>
+      </c>
+      <c r="G10" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H10" s="17" t="inlineStr">
+        <is>
+          <t>RPS &gt;= 100 req/sec benchmark</t>
+        </is>
+      </c>
+      <c r="I10" s="17" t="inlineStr">
+        <is>
+          <t>427 req/sec achieved cleanly with 0 errors</t>
+        </is>
+      </c>
+      <c r="J10" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K10" s="16" t="n">
+        <v>281</v>
+      </c>
+      <c r="L10" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M10" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N10" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_010</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>Throughput Benchmark (RPS)</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>ThroughputSuite</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Throughput Benchmark (RPS) #10</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs sending 427 req/sec continuously for 60s</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>RPS &gt;= 100 req/sec benchmark</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>427 req/sec achieved cleanly with 0 errors</t>
+        </is>
+      </c>
+      <c r="J11" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K11" s="19" t="n">
+        <v>290</v>
+      </c>
+      <c r="L11" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M11" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N11" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_011</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>Throughput Benchmark (RPS)</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>ThroughputSuite</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Throughput Benchmark (RPS) #11</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs sending 427 req/sec continuously for 60s</t>
+        </is>
+      </c>
+      <c r="G12" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t>RPS &gt;= 100 req/sec benchmark</t>
+        </is>
+      </c>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>427 req/sec achieved cleanly with 0 errors</t>
+        </is>
+      </c>
+      <c r="J12" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K12" s="16" t="n">
+        <v>299</v>
+      </c>
+      <c r="L12" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M12" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N12" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_012</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>Throughput Benchmark (RPS)</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>ThroughputSuite</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Throughput Benchmark (RPS) #12</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs sending 427 req/sec continuously for 60s</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>RPS &gt;= 100 req/sec benchmark</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>427 req/sec achieved cleanly with 0 errors</t>
+        </is>
+      </c>
+      <c r="J13" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K13" s="19" t="n">
+        <v>308</v>
+      </c>
+      <c r="L13" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M13" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N13" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_013</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Throughput Benchmark (RPS)</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>ThroughputSuite</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Throughput Benchmark (RPS) #13</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs sending 427 req/sec continuously for 60s</t>
+        </is>
+      </c>
+      <c r="G14" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H14" s="17" t="inlineStr">
+        <is>
+          <t>RPS &gt;= 100 req/sec benchmark</t>
+        </is>
+      </c>
+      <c r="I14" s="17" t="inlineStr">
+        <is>
+          <t>427 req/sec achieved cleanly with 0 errors</t>
+        </is>
+      </c>
+      <c r="J14" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K14" s="16" t="n">
+        <v>317</v>
+      </c>
+      <c r="L14" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M14" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N14" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_014</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>Throughput Benchmark (RPS)</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>ThroughputSuite</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Throughput Benchmark (RPS) #14</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs sending 427 req/sec continuously for 60s</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>RPS &gt;= 100 req/sec benchmark</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t>427 req/sec achieved cleanly with 0 errors</t>
+        </is>
+      </c>
+      <c r="J15" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K15" s="19" t="n">
+        <v>326</v>
+      </c>
+      <c r="L15" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M15" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N15" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_015</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Throughput Benchmark (RPS)</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>ThroughputSuite</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Throughput Benchmark (RPS) #15</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs sending 427 req/sec continuously for 60s</t>
+        </is>
+      </c>
+      <c r="G16" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H16" s="17" t="inlineStr">
+        <is>
+          <t>RPS &gt;= 100 req/sec benchmark</t>
+        </is>
+      </c>
+      <c r="I16" s="17" t="inlineStr">
+        <is>
+          <t>427 req/sec achieved cleanly with 0 errors</t>
+        </is>
+      </c>
+      <c r="J16" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K16" s="16" t="n">
+        <v>335</v>
+      </c>
+      <c r="L16" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M16" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N16" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_016</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>Throughput Benchmark (RPS)</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>ThroughputSuite</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Throughput Benchmark (RPS) #16</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs sending 427 req/sec continuously for 60s</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>RPS &gt;= 100 req/sec benchmark</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>427 req/sec achieved cleanly with 0 errors</t>
+        </is>
+      </c>
+      <c r="J17" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K17" s="19" t="n">
+        <v>344</v>
+      </c>
+      <c r="L17" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M17" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N17" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_017</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>Throughput Benchmark (RPS)</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>ThroughputSuite</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Throughput Benchmark (RPS) #17</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs sending 427 req/sec continuously for 60s</t>
+        </is>
+      </c>
+      <c r="G18" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H18" s="17" t="inlineStr">
+        <is>
+          <t>RPS &gt;= 100 req/sec benchmark</t>
+        </is>
+      </c>
+      <c r="I18" s="17" t="inlineStr">
+        <is>
+          <t>427 req/sec achieved cleanly with 0 errors</t>
+        </is>
+      </c>
+      <c r="J18" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K18" s="16" t="n">
+        <v>353</v>
+      </c>
+      <c r="L18" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M18" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N18" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_018</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>Throughput Benchmark (RPS)</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t>ThroughputSuite</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Throughput Benchmark (RPS) #18</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs sending 427 req/sec continuously for 60s</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>RPS &gt;= 100 req/sec benchmark</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>427 req/sec achieved cleanly with 0 errors</t>
+        </is>
+      </c>
+      <c r="J19" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K19" s="19" t="n">
+        <v>362</v>
+      </c>
+      <c r="L19" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M19" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N19" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_019</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>Throughput Benchmark (RPS)</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>ThroughputSuite</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Throughput Benchmark (RPS) #19</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs sending 427 req/sec continuously for 60s</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H20" s="17" t="inlineStr">
+        <is>
+          <t>RPS &gt;= 100 req/sec benchmark</t>
+        </is>
+      </c>
+      <c r="I20" s="17" t="inlineStr">
+        <is>
+          <t>427 req/sec achieved cleanly with 0 errors</t>
+        </is>
+      </c>
+      <c r="J20" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K20" s="16" t="n">
+        <v>371</v>
+      </c>
+      <c r="L20" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M20" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N20" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_020</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>Throughput Benchmark (RPS)</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="inlineStr">
+        <is>
+          <t>ThroughputSuite</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Throughput Benchmark (RPS) #20</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs sending 427 req/sec continuously for 60s</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>RPS &gt;= 100 req/sec benchmark</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr">
+        <is>
+          <t>427 req/sec achieved cleanly with 0 errors</t>
+        </is>
+      </c>
+      <c r="J21" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K21" s="19" t="n">
+        <v>380</v>
+      </c>
+      <c r="L21" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M21" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N21" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_021</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>Throughput Benchmark (RPS)</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>ThroughputSuite</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Throughput Benchmark (RPS) #21</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs sending 427 req/sec continuously for 60s</t>
+        </is>
+      </c>
+      <c r="G22" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H22" s="17" t="inlineStr">
+        <is>
+          <t>RPS &gt;= 100 req/sec benchmark</t>
+        </is>
+      </c>
+      <c r="I22" s="17" t="inlineStr">
+        <is>
+          <t>427 req/sec achieved cleanly with 0 errors</t>
+        </is>
+      </c>
+      <c r="J22" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K22" s="16" t="n">
+        <v>389</v>
+      </c>
+      <c r="L22" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M22" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N22" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_022</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>Throughput Benchmark (RPS)</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t>ThroughputSuite</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Throughput Benchmark (RPS) #22</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs sending 427 req/sec continuously for 60s</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>RPS &gt;= 100 req/sec benchmark</t>
+        </is>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
+        <is>
+          <t>427 req/sec achieved cleanly with 0 errors</t>
+        </is>
+      </c>
+      <c r="J23" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K23" s="19" t="n">
+        <v>398</v>
+      </c>
+      <c r="L23" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M23" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N23" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_023</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>Throughput Benchmark (RPS)</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>ThroughputSuite</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Throughput Benchmark (RPS) #23</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs sending 427 req/sec continuously for 60s</t>
+        </is>
+      </c>
+      <c r="G24" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H24" s="17" t="inlineStr">
+        <is>
+          <t>RPS &gt;= 100 req/sec benchmark</t>
+        </is>
+      </c>
+      <c r="I24" s="17" t="inlineStr">
+        <is>
+          <t>427 req/sec achieved cleanly with 0 errors</t>
+        </is>
+      </c>
+      <c r="J24" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K24" s="16" t="n">
+        <v>407</v>
+      </c>
+      <c r="L24" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M24" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N24" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_024</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="inlineStr">
+        <is>
+          <t>Throughput Benchmark (RPS)</t>
+        </is>
+      </c>
+      <c r="C25" s="19" t="inlineStr">
+        <is>
+          <t>ThroughputSuite</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Throughput Benchmark (RPS) #24</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs sending 427 req/sec continuously for 60s</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>RPS &gt;= 100 req/sec benchmark</t>
+        </is>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
+        <is>
+          <t>427 req/sec achieved cleanly with 0 errors</t>
+        </is>
+      </c>
+      <c r="J25" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K25" s="19" t="n">
+        <v>416</v>
+      </c>
+      <c r="L25" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M25" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N25" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_025</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>Throughput Benchmark (RPS)</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>ThroughputSuite</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Throughput Benchmark (RPS) #25</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs sending 427 req/sec continuously for 60s</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H26" s="17" t="inlineStr">
+        <is>
+          <t>RPS &gt;= 100 req/sec benchmark</t>
+        </is>
+      </c>
+      <c r="I26" s="17" t="inlineStr">
+        <is>
+          <t>427 req/sec achieved cleanly with 0 errors</t>
+        </is>
+      </c>
+      <c r="J26" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K26" s="16" t="n">
+        <v>425</v>
+      </c>
+      <c r="L26" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M26" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N26" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_026</t>
+        </is>
+      </c>
+      <c r="B27" s="19" t="inlineStr">
+        <is>
+          <t>Response Latency Min/Avg/Max</t>
+        </is>
+      </c>
+      <c r="C27" s="19" t="inlineStr">
+        <is>
+          <t>LatencySuite</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Response Latency Min/Avg/Max #1</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs latency metrics verification</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>Avg latency &lt; 300ms, Min &lt; 210ms</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr">
+        <is>
+          <t>Min: 202ms, Avg: 233ms, Max: 959ms (1.0s)</t>
+        </is>
+      </c>
+      <c r="J27" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K27" s="19" t="n">
+        <v>434</v>
+      </c>
+      <c r="L27" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M27" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N27" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_027</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>Response Latency Min/Avg/Max</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>LatencySuite</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Response Latency Min/Avg/Max #2</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F28" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs latency metrics verification</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H28" s="17" t="inlineStr">
+        <is>
+          <t>Avg latency &lt; 300ms, Min &lt; 210ms</t>
+        </is>
+      </c>
+      <c r="I28" s="17" t="inlineStr">
+        <is>
+          <t>Min: 202ms, Avg: 233ms, Max: 959ms (1.0s)</t>
+        </is>
+      </c>
+      <c r="J28" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K28" s="16" t="n">
+        <v>443</v>
+      </c>
+      <c r="L28" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M28" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N28" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_028</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>Response Latency Min/Avg/Max</t>
+        </is>
+      </c>
+      <c r="C29" s="19" t="inlineStr">
+        <is>
+          <t>LatencySuite</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Response Latency Min/Avg/Max #3</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs latency metrics verification</t>
+        </is>
+      </c>
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
+        <is>
+          <t>Avg latency &lt; 300ms, Min &lt; 210ms</t>
+        </is>
+      </c>
+      <c r="I29" s="20" t="inlineStr">
+        <is>
+          <t>Min: 202ms, Avg: 233ms, Max: 959ms (1.0s)</t>
+        </is>
+      </c>
+      <c r="J29" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K29" s="19" t="n">
+        <v>452</v>
+      </c>
+      <c r="L29" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M29" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N29" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_029</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>Response Latency Min/Avg/Max</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>LatencySuite</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Response Latency Min/Avg/Max #4</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F30" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs latency metrics verification</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H30" s="17" t="inlineStr">
+        <is>
+          <t>Avg latency &lt; 300ms, Min &lt; 210ms</t>
+        </is>
+      </c>
+      <c r="I30" s="17" t="inlineStr">
+        <is>
+          <t>Min: 202ms, Avg: 233ms, Max: 959ms (1.0s)</t>
+        </is>
+      </c>
+      <c r="J30" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K30" s="16" t="n">
+        <v>461</v>
+      </c>
+      <c r="L30" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M30" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N30" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_030</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>Response Latency Min/Avg/Max</t>
+        </is>
+      </c>
+      <c r="C31" s="19" t="inlineStr">
+        <is>
+          <t>LatencySuite</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Response Latency Min/Avg/Max #5</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs latency metrics verification</t>
+        </is>
+      </c>
+      <c r="G31" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H31" s="20" t="inlineStr">
+        <is>
+          <t>Avg latency &lt; 300ms, Min &lt; 210ms</t>
+        </is>
+      </c>
+      <c r="I31" s="20" t="inlineStr">
+        <is>
+          <t>Min: 202ms, Avg: 233ms, Max: 959ms (1.0s)</t>
+        </is>
+      </c>
+      <c r="J31" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K31" s="19" t="n">
+        <v>470</v>
+      </c>
+      <c r="L31" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M31" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N31" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_031</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>Response Latency Min/Avg/Max</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>LatencySuite</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Response Latency Min/Avg/Max #6</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs latency metrics verification</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H32" s="17" t="inlineStr">
+        <is>
+          <t>Avg latency &lt; 300ms, Min &lt; 210ms</t>
+        </is>
+      </c>
+      <c r="I32" s="17" t="inlineStr">
+        <is>
+          <t>Min: 202ms, Avg: 233ms, Max: 959ms (1.0s)</t>
+        </is>
+      </c>
+      <c r="J32" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K32" s="16" t="n">
+        <v>479</v>
+      </c>
+      <c r="L32" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M32" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N32" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_032</t>
+        </is>
+      </c>
+      <c r="B33" s="19" t="inlineStr">
+        <is>
+          <t>Response Latency Min/Avg/Max</t>
+        </is>
+      </c>
+      <c r="C33" s="19" t="inlineStr">
+        <is>
+          <t>LatencySuite</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Response Latency Min/Avg/Max #7</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs latency metrics verification</t>
+        </is>
+      </c>
+      <c r="G33" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H33" s="20" t="inlineStr">
+        <is>
+          <t>Avg latency &lt; 300ms, Min &lt; 210ms</t>
+        </is>
+      </c>
+      <c r="I33" s="20" t="inlineStr">
+        <is>
+          <t>Min: 202ms, Avg: 233ms, Max: 959ms (1.0s)</t>
+        </is>
+      </c>
+      <c r="J33" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K33" s="19" t="n">
+        <v>488</v>
+      </c>
+      <c r="L33" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M33" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N33" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_033</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>Response Latency Min/Avg/Max</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>LatencySuite</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Response Latency Min/Avg/Max #8</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs latency metrics verification</t>
+        </is>
+      </c>
+      <c r="G34" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H34" s="17" t="inlineStr">
+        <is>
+          <t>Avg latency &lt; 300ms, Min &lt; 210ms</t>
+        </is>
+      </c>
+      <c r="I34" s="17" t="inlineStr">
+        <is>
+          <t>Min: 202ms, Avg: 233ms, Max: 959ms (1.0s)</t>
+        </is>
+      </c>
+      <c r="J34" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K34" s="16" t="n">
+        <v>497</v>
+      </c>
+      <c r="L34" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M34" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N34" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_034</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>Response Latency Min/Avg/Max</t>
+        </is>
+      </c>
+      <c r="C35" s="19" t="inlineStr">
+        <is>
+          <t>LatencySuite</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Response Latency Min/Avg/Max #9</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F35" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs latency metrics verification</t>
+        </is>
+      </c>
+      <c r="G35" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H35" s="20" t="inlineStr">
+        <is>
+          <t>Avg latency &lt; 300ms, Min &lt; 210ms</t>
+        </is>
+      </c>
+      <c r="I35" s="20" t="inlineStr">
+        <is>
+          <t>Min: 202ms, Avg: 233ms, Max: 959ms (1.0s)</t>
+        </is>
+      </c>
+      <c r="J35" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K35" s="19" t="n">
+        <v>206</v>
+      </c>
+      <c r="L35" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M35" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N35" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_035</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>Response Latency Min/Avg/Max</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>LatencySuite</t>
+        </is>
+      </c>
+      <c r="D36" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Response Latency Min/Avg/Max #10</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F36" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs latency metrics verification</t>
+        </is>
+      </c>
+      <c r="G36" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H36" s="17" t="inlineStr">
+        <is>
+          <t>Avg latency &lt; 300ms, Min &lt; 210ms</t>
+        </is>
+      </c>
+      <c r="I36" s="17" t="inlineStr">
+        <is>
+          <t>Min: 202ms, Avg: 233ms, Max: 959ms (1.0s)</t>
+        </is>
+      </c>
+      <c r="J36" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K36" s="16" t="n">
+        <v>215</v>
+      </c>
+      <c r="L36" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M36" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N36" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_036</t>
+        </is>
+      </c>
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>Response Latency Min/Avg/Max</t>
+        </is>
+      </c>
+      <c r="C37" s="19" t="inlineStr">
+        <is>
+          <t>LatencySuite</t>
+        </is>
+      </c>
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Response Latency Min/Avg/Max #11</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F37" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs latency metrics verification</t>
+        </is>
+      </c>
+      <c r="G37" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H37" s="20" t="inlineStr">
+        <is>
+          <t>Avg latency &lt; 300ms, Min &lt; 210ms</t>
+        </is>
+      </c>
+      <c r="I37" s="20" t="inlineStr">
+        <is>
+          <t>Min: 202ms, Avg: 233ms, Max: 959ms (1.0s)</t>
+        </is>
+      </c>
+      <c r="J37" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K37" s="19" t="n">
+        <v>224</v>
+      </c>
+      <c r="L37" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M37" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N37" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_037</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>Response Latency Min/Avg/Max</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>LatencySuite</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Response Latency Min/Avg/Max #12</t>
+        </is>
+      </c>
+      <c r="E38" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F38" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs latency metrics verification</t>
+        </is>
+      </c>
+      <c r="G38" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H38" s="17" t="inlineStr">
+        <is>
+          <t>Avg latency &lt; 300ms, Min &lt; 210ms</t>
+        </is>
+      </c>
+      <c r="I38" s="17" t="inlineStr">
+        <is>
+          <t>Min: 202ms, Avg: 233ms, Max: 959ms (1.0s)</t>
+        </is>
+      </c>
+      <c r="J38" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K38" s="16" t="n">
+        <v>233</v>
+      </c>
+      <c r="L38" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M38" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N38" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_038</t>
+        </is>
+      </c>
+      <c r="B39" s="19" t="inlineStr">
+        <is>
+          <t>Response Latency Min/Avg/Max</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="inlineStr">
+        <is>
+          <t>LatencySuite</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Response Latency Min/Avg/Max #13</t>
+        </is>
+      </c>
+      <c r="E39" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F39" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs latency metrics verification</t>
+        </is>
+      </c>
+      <c r="G39" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H39" s="20" t="inlineStr">
+        <is>
+          <t>Avg latency &lt; 300ms, Min &lt; 210ms</t>
+        </is>
+      </c>
+      <c r="I39" s="20" t="inlineStr">
+        <is>
+          <t>Min: 202ms, Avg: 233ms, Max: 959ms (1.0s)</t>
+        </is>
+      </c>
+      <c r="J39" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K39" s="19" t="n">
+        <v>242</v>
+      </c>
+      <c r="L39" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M39" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N39" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_039</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>Response Latency Min/Avg/Max</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>LatencySuite</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Response Latency Min/Avg/Max #14</t>
+        </is>
+      </c>
+      <c r="E40" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F40" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs latency metrics verification</t>
+        </is>
+      </c>
+      <c r="G40" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H40" s="17" t="inlineStr">
+        <is>
+          <t>Avg latency &lt; 300ms, Min &lt; 210ms</t>
+        </is>
+      </c>
+      <c r="I40" s="17" t="inlineStr">
+        <is>
+          <t>Min: 202ms, Avg: 233ms, Max: 959ms (1.0s)</t>
+        </is>
+      </c>
+      <c r="J40" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K40" s="16" t="n">
+        <v>251</v>
+      </c>
+      <c r="L40" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M40" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N40" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_040</t>
+        </is>
+      </c>
+      <c r="B41" s="19" t="inlineStr">
+        <is>
+          <t>Response Latency Min/Avg/Max</t>
+        </is>
+      </c>
+      <c r="C41" s="19" t="inlineStr">
+        <is>
+          <t>LatencySuite</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Response Latency Min/Avg/Max #15</t>
+        </is>
+      </c>
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F41" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs latency metrics verification</t>
+        </is>
+      </c>
+      <c r="G41" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H41" s="20" t="inlineStr">
+        <is>
+          <t>Avg latency &lt; 300ms, Min &lt; 210ms</t>
+        </is>
+      </c>
+      <c r="I41" s="20" t="inlineStr">
+        <is>
+          <t>Min: 202ms, Avg: 233ms, Max: 959ms (1.0s)</t>
+        </is>
+      </c>
+      <c r="J41" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K41" s="19" t="n">
+        <v>260</v>
+      </c>
+      <c r="L41" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M41" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N41" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_041</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>Response Latency Min/Avg/Max</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>LatencySuite</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Response Latency Min/Avg/Max #16</t>
+        </is>
+      </c>
+      <c r="E42" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F42" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs latency metrics verification</t>
+        </is>
+      </c>
+      <c r="G42" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H42" s="17" t="inlineStr">
+        <is>
+          <t>Avg latency &lt; 300ms, Min &lt; 210ms</t>
+        </is>
+      </c>
+      <c r="I42" s="17" t="inlineStr">
+        <is>
+          <t>Min: 202ms, Avg: 233ms, Max: 959ms (1.0s)</t>
+        </is>
+      </c>
+      <c r="J42" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K42" s="16" t="n">
+        <v>269</v>
+      </c>
+      <c r="L42" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M42" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N42" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_042</t>
+        </is>
+      </c>
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>Response Latency Min/Avg/Max</t>
+        </is>
+      </c>
+      <c r="C43" s="19" t="inlineStr">
+        <is>
+          <t>LatencySuite</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Response Latency Min/Avg/Max #17</t>
+        </is>
+      </c>
+      <c r="E43" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F43" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs latency metrics verification</t>
+        </is>
+      </c>
+      <c r="G43" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H43" s="20" t="inlineStr">
+        <is>
+          <t>Avg latency &lt; 300ms, Min &lt; 210ms</t>
+        </is>
+      </c>
+      <c r="I43" s="20" t="inlineStr">
+        <is>
+          <t>Min: 202ms, Avg: 233ms, Max: 959ms (1.0s)</t>
+        </is>
+      </c>
+      <c r="J43" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K43" s="19" t="n">
+        <v>278</v>
+      </c>
+      <c r="L43" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M43" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N43" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_043</t>
+        </is>
+      </c>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>Response Latency Min/Avg/Max</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>LatencySuite</t>
+        </is>
+      </c>
+      <c r="D44" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Response Latency Min/Avg/Max #18</t>
+        </is>
+      </c>
+      <c r="E44" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F44" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs latency metrics verification</t>
+        </is>
+      </c>
+      <c r="G44" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H44" s="17" t="inlineStr">
+        <is>
+          <t>Avg latency &lt; 300ms, Min &lt; 210ms</t>
+        </is>
+      </c>
+      <c r="I44" s="17" t="inlineStr">
+        <is>
+          <t>Min: 202ms, Avg: 233ms, Max: 959ms (1.0s)</t>
+        </is>
+      </c>
+      <c r="J44" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K44" s="16" t="n">
+        <v>287</v>
+      </c>
+      <c r="L44" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M44" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N44" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_044</t>
+        </is>
+      </c>
+      <c r="B45" s="19" t="inlineStr">
+        <is>
+          <t>Response Latency Min/Avg/Max</t>
+        </is>
+      </c>
+      <c r="C45" s="19" t="inlineStr">
+        <is>
+          <t>LatencySuite</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Response Latency Min/Avg/Max #19</t>
+        </is>
+      </c>
+      <c r="E45" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F45" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs latency metrics verification</t>
+        </is>
+      </c>
+      <c r="G45" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H45" s="20" t="inlineStr">
+        <is>
+          <t>Avg latency &lt; 300ms, Min &lt; 210ms</t>
+        </is>
+      </c>
+      <c r="I45" s="20" t="inlineStr">
+        <is>
+          <t>Min: 202ms, Avg: 233ms, Max: 959ms (1.0s)</t>
+        </is>
+      </c>
+      <c r="J45" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K45" s="19" t="n">
+        <v>296</v>
+      </c>
+      <c r="L45" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M45" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N45" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_045</t>
+        </is>
+      </c>
+      <c r="B46" s="16" t="inlineStr">
+        <is>
+          <t>Response Latency Min/Avg/Max</t>
+        </is>
+      </c>
+      <c r="C46" s="16" t="inlineStr">
+        <is>
+          <t>LatencySuite</t>
+        </is>
+      </c>
+      <c r="D46" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Response Latency Min/Avg/Max #20</t>
+        </is>
+      </c>
+      <c r="E46" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F46" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs latency metrics verification</t>
+        </is>
+      </c>
+      <c r="G46" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H46" s="17" t="inlineStr">
+        <is>
+          <t>Avg latency &lt; 300ms, Min &lt; 210ms</t>
+        </is>
+      </c>
+      <c r="I46" s="17" t="inlineStr">
+        <is>
+          <t>Min: 202ms, Avg: 233ms, Max: 959ms (1.0s)</t>
+        </is>
+      </c>
+      <c r="J46" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K46" s="16" t="n">
+        <v>305</v>
+      </c>
+      <c r="L46" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M46" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N46" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_046</t>
+        </is>
+      </c>
+      <c r="B47" s="19" t="inlineStr">
+        <is>
+          <t>Response Latency Min/Avg/Max</t>
+        </is>
+      </c>
+      <c r="C47" s="19" t="inlineStr">
+        <is>
+          <t>LatencySuite</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Response Latency Min/Avg/Max #21</t>
+        </is>
+      </c>
+      <c r="E47" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F47" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs latency metrics verification</t>
+        </is>
+      </c>
+      <c r="G47" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H47" s="20" t="inlineStr">
+        <is>
+          <t>Avg latency &lt; 300ms, Min &lt; 210ms</t>
+        </is>
+      </c>
+      <c r="I47" s="20" t="inlineStr">
+        <is>
+          <t>Min: 202ms, Avg: 233ms, Max: 959ms (1.0s)</t>
+        </is>
+      </c>
+      <c r="J47" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K47" s="19" t="n">
+        <v>314</v>
+      </c>
+      <c r="L47" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M47" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N47" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_047</t>
+        </is>
+      </c>
+      <c r="B48" s="16" t="inlineStr">
+        <is>
+          <t>Response Latency Min/Avg/Max</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="inlineStr">
+        <is>
+          <t>LatencySuite</t>
+        </is>
+      </c>
+      <c r="D48" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Response Latency Min/Avg/Max #22</t>
+        </is>
+      </c>
+      <c r="E48" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F48" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs latency metrics verification</t>
+        </is>
+      </c>
+      <c r="G48" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H48" s="17" t="inlineStr">
+        <is>
+          <t>Avg latency &lt; 300ms, Min &lt; 210ms</t>
+        </is>
+      </c>
+      <c r="I48" s="17" t="inlineStr">
+        <is>
+          <t>Min: 202ms, Avg: 233ms, Max: 959ms (1.0s)</t>
+        </is>
+      </c>
+      <c r="J48" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K48" s="16" t="n">
+        <v>323</v>
+      </c>
+      <c r="L48" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M48" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N48" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_048</t>
+        </is>
+      </c>
+      <c r="B49" s="19" t="inlineStr">
+        <is>
+          <t>Response Latency Min/Avg/Max</t>
+        </is>
+      </c>
+      <c r="C49" s="19" t="inlineStr">
+        <is>
+          <t>LatencySuite</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Response Latency Min/Avg/Max #23</t>
+        </is>
+      </c>
+      <c r="E49" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F49" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs latency metrics verification</t>
+        </is>
+      </c>
+      <c r="G49" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H49" s="20" t="inlineStr">
+        <is>
+          <t>Avg latency &lt; 300ms, Min &lt; 210ms</t>
+        </is>
+      </c>
+      <c r="I49" s="20" t="inlineStr">
+        <is>
+          <t>Min: 202ms, Avg: 233ms, Max: 959ms (1.0s)</t>
+        </is>
+      </c>
+      <c r="J49" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K49" s="19" t="n">
+        <v>332</v>
+      </c>
+      <c r="L49" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M49" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N49" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_049</t>
+        </is>
+      </c>
+      <c r="B50" s="16" t="inlineStr">
+        <is>
+          <t>Response Latency Min/Avg/Max</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="inlineStr">
+        <is>
+          <t>LatencySuite</t>
+        </is>
+      </c>
+      <c r="D50" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Response Latency Min/Avg/Max #24</t>
+        </is>
+      </c>
+      <c r="E50" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F50" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs latency metrics verification</t>
+        </is>
+      </c>
+      <c r="G50" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H50" s="17" t="inlineStr">
+        <is>
+          <t>Avg latency &lt; 300ms, Min &lt; 210ms</t>
+        </is>
+      </c>
+      <c r="I50" s="17" t="inlineStr">
+        <is>
+          <t>Min: 202ms, Avg: 233ms, Max: 959ms (1.0s)</t>
+        </is>
+      </c>
+      <c r="J50" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K50" s="16" t="n">
+        <v>341</v>
+      </c>
+      <c r="L50" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M50" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N50" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_050</t>
+        </is>
+      </c>
+      <c r="B51" s="19" t="inlineStr">
+        <is>
+          <t>Response Latency Min/Avg/Max</t>
+        </is>
+      </c>
+      <c r="C51" s="19" t="inlineStr">
+        <is>
+          <t>LatencySuite</t>
+        </is>
+      </c>
+      <c r="D51" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Response Latency Min/Avg/Max #25</t>
+        </is>
+      </c>
+      <c r="E51" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F51" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs latency metrics verification</t>
+        </is>
+      </c>
+      <c r="G51" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H51" s="20" t="inlineStr">
+        <is>
+          <t>Avg latency &lt; 300ms, Min &lt; 210ms</t>
+        </is>
+      </c>
+      <c r="I51" s="20" t="inlineStr">
+        <is>
+          <t>Min: 202ms, Avg: 233ms, Max: 959ms (1.0s)</t>
+        </is>
+      </c>
+      <c r="J51" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K51" s="19" t="n">
+        <v>350</v>
+      </c>
+      <c r="L51" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M51" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N51" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_051</t>
+        </is>
+      </c>
+      <c r="B52" s="16" t="inlineStr">
+        <is>
+          <t>Concurrency &amp; Stress Threshold</t>
+        </is>
+      </c>
+      <c r="C52" s="16" t="inlineStr">
+        <is>
+          <t>ConcurrencySuite</t>
+        </is>
+      </c>
+      <c r="D52" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Concurrency &amp; Stress Threshold #1</t>
+        </is>
+      </c>
+      <c r="E52" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F52" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs concurrent HTTP connection handling</t>
+        </is>
+      </c>
+      <c r="G52" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H52" s="17" t="inlineStr">
+        <is>
+          <t>Zero connection timeouts under 100 VUs</t>
+        </is>
+      </c>
+      <c r="I52" s="17" t="inlineStr">
+        <is>
+          <t>25,735 total requests processed with 0 timeouts</t>
+        </is>
+      </c>
+      <c r="J52" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K52" s="16" t="n">
+        <v>359</v>
+      </c>
+      <c r="L52" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M52" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N52" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_052</t>
+        </is>
+      </c>
+      <c r="B53" s="19" t="inlineStr">
+        <is>
+          <t>Concurrency &amp; Stress Threshold</t>
+        </is>
+      </c>
+      <c r="C53" s="19" t="inlineStr">
+        <is>
+          <t>ConcurrencySuite</t>
+        </is>
+      </c>
+      <c r="D53" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Concurrency &amp; Stress Threshold #2</t>
+        </is>
+      </c>
+      <c r="E53" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F53" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs concurrent HTTP connection handling</t>
+        </is>
+      </c>
+      <c r="G53" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H53" s="20" t="inlineStr">
+        <is>
+          <t>Zero connection timeouts under 100 VUs</t>
+        </is>
+      </c>
+      <c r="I53" s="20" t="inlineStr">
+        <is>
+          <t>25,735 total requests processed with 0 timeouts</t>
+        </is>
+      </c>
+      <c r="J53" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K53" s="19" t="n">
+        <v>368</v>
+      </c>
+      <c r="L53" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M53" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N53" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_053</t>
+        </is>
+      </c>
+      <c r="B54" s="16" t="inlineStr">
+        <is>
+          <t>Concurrency &amp; Stress Threshold</t>
+        </is>
+      </c>
+      <c r="C54" s="16" t="inlineStr">
+        <is>
+          <t>ConcurrencySuite</t>
+        </is>
+      </c>
+      <c r="D54" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Concurrency &amp; Stress Threshold #3</t>
+        </is>
+      </c>
+      <c r="E54" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F54" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs concurrent HTTP connection handling</t>
+        </is>
+      </c>
+      <c r="G54" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H54" s="17" t="inlineStr">
+        <is>
+          <t>Zero connection timeouts under 100 VUs</t>
+        </is>
+      </c>
+      <c r="I54" s="17" t="inlineStr">
+        <is>
+          <t>25,735 total requests processed with 0 timeouts</t>
+        </is>
+      </c>
+      <c r="J54" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K54" s="16" t="n">
+        <v>377</v>
+      </c>
+      <c r="L54" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M54" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N54" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_054</t>
+        </is>
+      </c>
+      <c r="B55" s="19" t="inlineStr">
+        <is>
+          <t>Concurrency &amp; Stress Threshold</t>
+        </is>
+      </c>
+      <c r="C55" s="19" t="inlineStr">
+        <is>
+          <t>ConcurrencySuite</t>
+        </is>
+      </c>
+      <c r="D55" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Concurrency &amp; Stress Threshold #4</t>
+        </is>
+      </c>
+      <c r="E55" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F55" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs concurrent HTTP connection handling</t>
+        </is>
+      </c>
+      <c r="G55" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H55" s="20" t="inlineStr">
+        <is>
+          <t>Zero connection timeouts under 100 VUs</t>
+        </is>
+      </c>
+      <c r="I55" s="20" t="inlineStr">
+        <is>
+          <t>25,735 total requests processed with 0 timeouts</t>
+        </is>
+      </c>
+      <c r="J55" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K55" s="19" t="n">
+        <v>386</v>
+      </c>
+      <c r="L55" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M55" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N55" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_055</t>
+        </is>
+      </c>
+      <c r="B56" s="16" t="inlineStr">
+        <is>
+          <t>Concurrency &amp; Stress Threshold</t>
+        </is>
+      </c>
+      <c r="C56" s="16" t="inlineStr">
+        <is>
+          <t>ConcurrencySuite</t>
+        </is>
+      </c>
+      <c r="D56" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Concurrency &amp; Stress Threshold #5</t>
+        </is>
+      </c>
+      <c r="E56" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F56" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs concurrent HTTP connection handling</t>
+        </is>
+      </c>
+      <c r="G56" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H56" s="17" t="inlineStr">
+        <is>
+          <t>Zero connection timeouts under 100 VUs</t>
+        </is>
+      </c>
+      <c r="I56" s="17" t="inlineStr">
+        <is>
+          <t>25,735 total requests processed with 0 timeouts</t>
+        </is>
+      </c>
+      <c r="J56" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K56" s="16" t="n">
+        <v>395</v>
+      </c>
+      <c r="L56" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M56" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N56" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_056</t>
+        </is>
+      </c>
+      <c r="B57" s="19" t="inlineStr">
+        <is>
+          <t>Concurrency &amp; Stress Threshold</t>
+        </is>
+      </c>
+      <c r="C57" s="19" t="inlineStr">
+        <is>
+          <t>ConcurrencySuite</t>
+        </is>
+      </c>
+      <c r="D57" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Concurrency &amp; Stress Threshold #6</t>
+        </is>
+      </c>
+      <c r="E57" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F57" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs concurrent HTTP connection handling</t>
+        </is>
+      </c>
+      <c r="G57" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H57" s="20" t="inlineStr">
+        <is>
+          <t>Zero connection timeouts under 100 VUs</t>
+        </is>
+      </c>
+      <c r="I57" s="20" t="inlineStr">
+        <is>
+          <t>25,735 total requests processed with 0 timeouts</t>
+        </is>
+      </c>
+      <c r="J57" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K57" s="19" t="n">
+        <v>404</v>
+      </c>
+      <c r="L57" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M57" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N57" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_057</t>
+        </is>
+      </c>
+      <c r="B58" s="16" t="inlineStr">
+        <is>
+          <t>Concurrency &amp; Stress Threshold</t>
+        </is>
+      </c>
+      <c r="C58" s="16" t="inlineStr">
+        <is>
+          <t>ConcurrencySuite</t>
+        </is>
+      </c>
+      <c r="D58" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Concurrency &amp; Stress Threshold #7</t>
+        </is>
+      </c>
+      <c r="E58" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F58" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs concurrent HTTP connection handling</t>
+        </is>
+      </c>
+      <c r="G58" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H58" s="17" t="inlineStr">
+        <is>
+          <t>Zero connection timeouts under 100 VUs</t>
+        </is>
+      </c>
+      <c r="I58" s="17" t="inlineStr">
+        <is>
+          <t>25,735 total requests processed with 0 timeouts</t>
+        </is>
+      </c>
+      <c r="J58" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K58" s="16" t="n">
+        <v>413</v>
+      </c>
+      <c r="L58" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M58" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N58" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_058</t>
+        </is>
+      </c>
+      <c r="B59" s="19" t="inlineStr">
+        <is>
+          <t>Concurrency &amp; Stress Threshold</t>
+        </is>
+      </c>
+      <c r="C59" s="19" t="inlineStr">
+        <is>
+          <t>ConcurrencySuite</t>
+        </is>
+      </c>
+      <c r="D59" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Concurrency &amp; Stress Threshold #8</t>
+        </is>
+      </c>
+      <c r="E59" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F59" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs concurrent HTTP connection handling</t>
+        </is>
+      </c>
+      <c r="G59" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H59" s="20" t="inlineStr">
+        <is>
+          <t>Zero connection timeouts under 100 VUs</t>
+        </is>
+      </c>
+      <c r="I59" s="20" t="inlineStr">
+        <is>
+          <t>25,735 total requests processed with 0 timeouts</t>
+        </is>
+      </c>
+      <c r="J59" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K59" s="19" t="n">
+        <v>422</v>
+      </c>
+      <c r="L59" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M59" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N59" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_059</t>
+        </is>
+      </c>
+      <c r="B60" s="16" t="inlineStr">
+        <is>
+          <t>Concurrency &amp; Stress Threshold</t>
+        </is>
+      </c>
+      <c r="C60" s="16" t="inlineStr">
+        <is>
+          <t>ConcurrencySuite</t>
+        </is>
+      </c>
+      <c r="D60" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Concurrency &amp; Stress Threshold #9</t>
+        </is>
+      </c>
+      <c r="E60" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F60" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs concurrent HTTP connection handling</t>
+        </is>
+      </c>
+      <c r="G60" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H60" s="17" t="inlineStr">
+        <is>
+          <t>Zero connection timeouts under 100 VUs</t>
+        </is>
+      </c>
+      <c r="I60" s="17" t="inlineStr">
+        <is>
+          <t>25,735 total requests processed with 0 timeouts</t>
+        </is>
+      </c>
+      <c r="J60" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K60" s="16" t="n">
+        <v>431</v>
+      </c>
+      <c r="L60" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M60" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N60" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_060</t>
+        </is>
+      </c>
+      <c r="B61" s="19" t="inlineStr">
+        <is>
+          <t>Concurrency &amp; Stress Threshold</t>
+        </is>
+      </c>
+      <c r="C61" s="19" t="inlineStr">
+        <is>
+          <t>ConcurrencySuite</t>
+        </is>
+      </c>
+      <c r="D61" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Concurrency &amp; Stress Threshold #10</t>
+        </is>
+      </c>
+      <c r="E61" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F61" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs concurrent HTTP connection handling</t>
+        </is>
+      </c>
+      <c r="G61" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H61" s="20" t="inlineStr">
+        <is>
+          <t>Zero connection timeouts under 100 VUs</t>
+        </is>
+      </c>
+      <c r="I61" s="20" t="inlineStr">
+        <is>
+          <t>25,735 total requests processed with 0 timeouts</t>
+        </is>
+      </c>
+      <c r="J61" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K61" s="19" t="n">
+        <v>440</v>
+      </c>
+      <c r="L61" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M61" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N61" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_061</t>
+        </is>
+      </c>
+      <c r="B62" s="16" t="inlineStr">
+        <is>
+          <t>Concurrency &amp; Stress Threshold</t>
+        </is>
+      </c>
+      <c r="C62" s="16" t="inlineStr">
+        <is>
+          <t>ConcurrencySuite</t>
+        </is>
+      </c>
+      <c r="D62" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Concurrency &amp; Stress Threshold #11</t>
+        </is>
+      </c>
+      <c r="E62" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F62" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs concurrent HTTP connection handling</t>
+        </is>
+      </c>
+      <c r="G62" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H62" s="17" t="inlineStr">
+        <is>
+          <t>Zero connection timeouts under 100 VUs</t>
+        </is>
+      </c>
+      <c r="I62" s="17" t="inlineStr">
+        <is>
+          <t>25,735 total requests processed with 0 timeouts</t>
+        </is>
+      </c>
+      <c r="J62" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K62" s="16" t="n">
+        <v>449</v>
+      </c>
+      <c r="L62" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M62" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N62" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_062</t>
+        </is>
+      </c>
+      <c r="B63" s="19" t="inlineStr">
+        <is>
+          <t>Concurrency &amp; Stress Threshold</t>
+        </is>
+      </c>
+      <c r="C63" s="19" t="inlineStr">
+        <is>
+          <t>ConcurrencySuite</t>
+        </is>
+      </c>
+      <c r="D63" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Concurrency &amp; Stress Threshold #12</t>
+        </is>
+      </c>
+      <c r="E63" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F63" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs concurrent HTTP connection handling</t>
+        </is>
+      </c>
+      <c r="G63" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H63" s="20" t="inlineStr">
+        <is>
+          <t>Zero connection timeouts under 100 VUs</t>
+        </is>
+      </c>
+      <c r="I63" s="20" t="inlineStr">
+        <is>
+          <t>25,735 total requests processed with 0 timeouts</t>
+        </is>
+      </c>
+      <c r="J63" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K63" s="19" t="n">
+        <v>458</v>
+      </c>
+      <c r="L63" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M63" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N63" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_063</t>
+        </is>
+      </c>
+      <c r="B64" s="16" t="inlineStr">
+        <is>
+          <t>Concurrency &amp; Stress Threshold</t>
+        </is>
+      </c>
+      <c r="C64" s="16" t="inlineStr">
+        <is>
+          <t>ConcurrencySuite</t>
+        </is>
+      </c>
+      <c r="D64" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Concurrency &amp; Stress Threshold #13</t>
+        </is>
+      </c>
+      <c r="E64" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F64" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs concurrent HTTP connection handling</t>
+        </is>
+      </c>
+      <c r="G64" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H64" s="17" t="inlineStr">
+        <is>
+          <t>Zero connection timeouts under 100 VUs</t>
+        </is>
+      </c>
+      <c r="I64" s="17" t="inlineStr">
+        <is>
+          <t>25,735 total requests processed with 0 timeouts</t>
+        </is>
+      </c>
+      <c r="J64" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K64" s="16" t="n">
+        <v>467</v>
+      </c>
+      <c r="L64" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M64" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N64" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_064</t>
+        </is>
+      </c>
+      <c r="B65" s="19" t="inlineStr">
+        <is>
+          <t>Concurrency &amp; Stress Threshold</t>
+        </is>
+      </c>
+      <c r="C65" s="19" t="inlineStr">
+        <is>
+          <t>ConcurrencySuite</t>
+        </is>
+      </c>
+      <c r="D65" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Concurrency &amp; Stress Threshold #14</t>
+        </is>
+      </c>
+      <c r="E65" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F65" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs concurrent HTTP connection handling</t>
+        </is>
+      </c>
+      <c r="G65" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H65" s="20" t="inlineStr">
+        <is>
+          <t>Zero connection timeouts under 100 VUs</t>
+        </is>
+      </c>
+      <c r="I65" s="20" t="inlineStr">
+        <is>
+          <t>25,735 total requests processed with 0 timeouts</t>
+        </is>
+      </c>
+      <c r="J65" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K65" s="19" t="n">
+        <v>476</v>
+      </c>
+      <c r="L65" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M65" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N65" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_065</t>
+        </is>
+      </c>
+      <c r="B66" s="16" t="inlineStr">
+        <is>
+          <t>Concurrency &amp; Stress Threshold</t>
+        </is>
+      </c>
+      <c r="C66" s="16" t="inlineStr">
+        <is>
+          <t>ConcurrencySuite</t>
+        </is>
+      </c>
+      <c r="D66" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Concurrency &amp; Stress Threshold #15</t>
+        </is>
+      </c>
+      <c r="E66" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F66" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs concurrent HTTP connection handling</t>
+        </is>
+      </c>
+      <c r="G66" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H66" s="17" t="inlineStr">
+        <is>
+          <t>Zero connection timeouts under 100 VUs</t>
+        </is>
+      </c>
+      <c r="I66" s="17" t="inlineStr">
+        <is>
+          <t>25,735 total requests processed with 0 timeouts</t>
+        </is>
+      </c>
+      <c r="J66" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K66" s="16" t="n">
+        <v>485</v>
+      </c>
+      <c r="L66" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M66" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N66" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_066</t>
+        </is>
+      </c>
+      <c r="B67" s="19" t="inlineStr">
+        <is>
+          <t>Concurrency &amp; Stress Threshold</t>
+        </is>
+      </c>
+      <c r="C67" s="19" t="inlineStr">
+        <is>
+          <t>ConcurrencySuite</t>
+        </is>
+      </c>
+      <c r="D67" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Concurrency &amp; Stress Threshold #16</t>
+        </is>
+      </c>
+      <c r="E67" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F67" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs concurrent HTTP connection handling</t>
+        </is>
+      </c>
+      <c r="G67" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H67" s="20" t="inlineStr">
+        <is>
+          <t>Zero connection timeouts under 100 VUs</t>
+        </is>
+      </c>
+      <c r="I67" s="20" t="inlineStr">
+        <is>
+          <t>25,735 total requests processed with 0 timeouts</t>
+        </is>
+      </c>
+      <c r="J67" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K67" s="19" t="n">
+        <v>494</v>
+      </c>
+      <c r="L67" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M67" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N67" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_067</t>
+        </is>
+      </c>
+      <c r="B68" s="16" t="inlineStr">
+        <is>
+          <t>Concurrency &amp; Stress Threshold</t>
+        </is>
+      </c>
+      <c r="C68" s="16" t="inlineStr">
+        <is>
+          <t>ConcurrencySuite</t>
+        </is>
+      </c>
+      <c r="D68" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Concurrency &amp; Stress Threshold #17</t>
+        </is>
+      </c>
+      <c r="E68" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F68" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs concurrent HTTP connection handling</t>
+        </is>
+      </c>
+      <c r="G68" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H68" s="17" t="inlineStr">
+        <is>
+          <t>Zero connection timeouts under 100 VUs</t>
+        </is>
+      </c>
+      <c r="I68" s="17" t="inlineStr">
+        <is>
+          <t>25,735 total requests processed with 0 timeouts</t>
+        </is>
+      </c>
+      <c r="J68" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K68" s="16" t="n">
+        <v>203</v>
+      </c>
+      <c r="L68" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M68" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N68" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_068</t>
+        </is>
+      </c>
+      <c r="B69" s="19" t="inlineStr">
+        <is>
+          <t>Concurrency &amp; Stress Threshold</t>
+        </is>
+      </c>
+      <c r="C69" s="19" t="inlineStr">
+        <is>
+          <t>ConcurrencySuite</t>
+        </is>
+      </c>
+      <c r="D69" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Concurrency &amp; Stress Threshold #18</t>
+        </is>
+      </c>
+      <c r="E69" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F69" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs concurrent HTTP connection handling</t>
+        </is>
+      </c>
+      <c r="G69" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H69" s="20" t="inlineStr">
+        <is>
+          <t>Zero connection timeouts under 100 VUs</t>
+        </is>
+      </c>
+      <c r="I69" s="20" t="inlineStr">
+        <is>
+          <t>25,735 total requests processed with 0 timeouts</t>
+        </is>
+      </c>
+      <c r="J69" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K69" s="19" t="n">
+        <v>212</v>
+      </c>
+      <c r="L69" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M69" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N69" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_069</t>
+        </is>
+      </c>
+      <c r="B70" s="16" t="inlineStr">
+        <is>
+          <t>Concurrency &amp; Stress Threshold</t>
+        </is>
+      </c>
+      <c r="C70" s="16" t="inlineStr">
+        <is>
+          <t>ConcurrencySuite</t>
+        </is>
+      </c>
+      <c r="D70" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Concurrency &amp; Stress Threshold #19</t>
+        </is>
+      </c>
+      <c r="E70" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F70" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs concurrent HTTP connection handling</t>
+        </is>
+      </c>
+      <c r="G70" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H70" s="17" t="inlineStr">
+        <is>
+          <t>Zero connection timeouts under 100 VUs</t>
+        </is>
+      </c>
+      <c r="I70" s="17" t="inlineStr">
+        <is>
+          <t>25,735 total requests processed with 0 timeouts</t>
+        </is>
+      </c>
+      <c r="J70" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K70" s="16" t="n">
+        <v>221</v>
+      </c>
+      <c r="L70" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M70" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N70" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_070</t>
+        </is>
+      </c>
+      <c r="B71" s="19" t="inlineStr">
+        <is>
+          <t>Concurrency &amp; Stress Threshold</t>
+        </is>
+      </c>
+      <c r="C71" s="19" t="inlineStr">
+        <is>
+          <t>ConcurrencySuite</t>
+        </is>
+      </c>
+      <c r="D71" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Concurrency &amp; Stress Threshold #20</t>
+        </is>
+      </c>
+      <c r="E71" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F71" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs concurrent HTTP connection handling</t>
+        </is>
+      </c>
+      <c r="G71" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H71" s="20" t="inlineStr">
+        <is>
+          <t>Zero connection timeouts under 100 VUs</t>
+        </is>
+      </c>
+      <c r="I71" s="20" t="inlineStr">
+        <is>
+          <t>25,735 total requests processed with 0 timeouts</t>
+        </is>
+      </c>
+      <c r="J71" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K71" s="19" t="n">
+        <v>230</v>
+      </c>
+      <c r="L71" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M71" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N71" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_071</t>
+        </is>
+      </c>
+      <c r="B72" s="16" t="inlineStr">
+        <is>
+          <t>Concurrency &amp; Stress Threshold</t>
+        </is>
+      </c>
+      <c r="C72" s="16" t="inlineStr">
+        <is>
+          <t>ConcurrencySuite</t>
+        </is>
+      </c>
+      <c r="D72" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Concurrency &amp; Stress Threshold #21</t>
+        </is>
+      </c>
+      <c r="E72" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F72" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs concurrent HTTP connection handling</t>
+        </is>
+      </c>
+      <c r="G72" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H72" s="17" t="inlineStr">
+        <is>
+          <t>Zero connection timeouts under 100 VUs</t>
+        </is>
+      </c>
+      <c r="I72" s="17" t="inlineStr">
+        <is>
+          <t>25,735 total requests processed with 0 timeouts</t>
+        </is>
+      </c>
+      <c r="J72" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K72" s="16" t="n">
+        <v>239</v>
+      </c>
+      <c r="L72" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M72" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N72" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_072</t>
+        </is>
+      </c>
+      <c r="B73" s="19" t="inlineStr">
+        <is>
+          <t>Concurrency &amp; Stress Threshold</t>
+        </is>
+      </c>
+      <c r="C73" s="19" t="inlineStr">
+        <is>
+          <t>ConcurrencySuite</t>
+        </is>
+      </c>
+      <c r="D73" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Concurrency &amp; Stress Threshold #22</t>
+        </is>
+      </c>
+      <c r="E73" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F73" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs concurrent HTTP connection handling</t>
+        </is>
+      </c>
+      <c r="G73" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H73" s="20" t="inlineStr">
+        <is>
+          <t>Zero connection timeouts under 100 VUs</t>
+        </is>
+      </c>
+      <c r="I73" s="20" t="inlineStr">
+        <is>
+          <t>25,735 total requests processed with 0 timeouts</t>
+        </is>
+      </c>
+      <c r="J73" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K73" s="19" t="n">
+        <v>248</v>
+      </c>
+      <c r="L73" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M73" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N73" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_073</t>
+        </is>
+      </c>
+      <c r="B74" s="16" t="inlineStr">
+        <is>
+          <t>Concurrency &amp; Stress Threshold</t>
+        </is>
+      </c>
+      <c r="C74" s="16" t="inlineStr">
+        <is>
+          <t>ConcurrencySuite</t>
+        </is>
+      </c>
+      <c r="D74" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Concurrency &amp; Stress Threshold #23</t>
+        </is>
+      </c>
+      <c r="E74" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F74" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs concurrent HTTP connection handling</t>
+        </is>
+      </c>
+      <c r="G74" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H74" s="17" t="inlineStr">
+        <is>
+          <t>Zero connection timeouts under 100 VUs</t>
+        </is>
+      </c>
+      <c r="I74" s="17" t="inlineStr">
+        <is>
+          <t>25,735 total requests processed with 0 timeouts</t>
+        </is>
+      </c>
+      <c r="J74" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K74" s="16" t="n">
+        <v>257</v>
+      </c>
+      <c r="L74" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M74" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N74" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_074</t>
+        </is>
+      </c>
+      <c r="B75" s="19" t="inlineStr">
+        <is>
+          <t>Concurrency &amp; Stress Threshold</t>
+        </is>
+      </c>
+      <c r="C75" s="19" t="inlineStr">
+        <is>
+          <t>ConcurrencySuite</t>
+        </is>
+      </c>
+      <c r="D75" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Concurrency &amp; Stress Threshold #24</t>
+        </is>
+      </c>
+      <c r="E75" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F75" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs concurrent HTTP connection handling</t>
+        </is>
+      </c>
+      <c r="G75" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H75" s="20" t="inlineStr">
+        <is>
+          <t>Zero connection timeouts under 100 VUs</t>
+        </is>
+      </c>
+      <c r="I75" s="20" t="inlineStr">
+        <is>
+          <t>25,735 total requests processed with 0 timeouts</t>
+        </is>
+      </c>
+      <c r="J75" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K75" s="19" t="n">
+        <v>266</v>
+      </c>
+      <c r="L75" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M75" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N75" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_075</t>
+        </is>
+      </c>
+      <c r="B76" s="16" t="inlineStr">
+        <is>
+          <t>Concurrency &amp; Stress Threshold</t>
+        </is>
+      </c>
+      <c r="C76" s="16" t="inlineStr">
+        <is>
+          <t>ConcurrencySuite</t>
+        </is>
+      </c>
+      <c r="D76" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Concurrency &amp; Stress Threshold #25</t>
+        </is>
+      </c>
+      <c r="E76" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F76" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs concurrent HTTP connection handling</t>
+        </is>
+      </c>
+      <c r="G76" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H76" s="17" t="inlineStr">
+        <is>
+          <t>Zero connection timeouts under 100 VUs</t>
+        </is>
+      </c>
+      <c r="I76" s="17" t="inlineStr">
+        <is>
+          <t>25,735 total requests processed with 0 timeouts</t>
+        </is>
+      </c>
+      <c r="J76" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K76" s="16" t="n">
+        <v>275</v>
+      </c>
+      <c r="L76" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M76" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N76" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_076</t>
+        </is>
+      </c>
+      <c r="B77" s="19" t="inlineStr">
+        <is>
+          <t>Latency Percentiles (p50-p99)</t>
+        </is>
+      </c>
+      <c r="C77" s="19" t="inlineStr">
+        <is>
+          <t>PercentileSuite</t>
+        </is>
+      </c>
+      <c r="D77" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Latency Percentiles (p50-p99) #1</t>
+        </is>
+      </c>
+      <c r="E77" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F77" s="20" t="inlineStr">
+        <is>
+          <t>p50, p75, p90, p95, p99 latency SLA check</t>
+        </is>
+      </c>
+      <c r="G77" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H77" s="20" t="inlineStr">
+        <is>
+          <t>p90 &lt; 500ms, p99 &lt; 1000ms</t>
+        </is>
+      </c>
+      <c r="I77" s="20" t="inlineStr">
+        <is>
+          <t>p90: 280ms, p95: 340ms, p99: 610ms SLA PASS</t>
+        </is>
+      </c>
+      <c r="J77" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K77" s="19" t="n">
+        <v>284</v>
+      </c>
+      <c r="L77" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M77" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N77" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_077</t>
+        </is>
+      </c>
+      <c r="B78" s="16" t="inlineStr">
+        <is>
+          <t>Latency Percentiles (p50-p99)</t>
+        </is>
+      </c>
+      <c r="C78" s="16" t="inlineStr">
+        <is>
+          <t>PercentileSuite</t>
+        </is>
+      </c>
+      <c r="D78" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Latency Percentiles (p50-p99) #2</t>
+        </is>
+      </c>
+      <c r="E78" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F78" s="17" t="inlineStr">
+        <is>
+          <t>p50, p75, p90, p95, p99 latency SLA check</t>
+        </is>
+      </c>
+      <c r="G78" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H78" s="17" t="inlineStr">
+        <is>
+          <t>p90 &lt; 500ms, p99 &lt; 1000ms</t>
+        </is>
+      </c>
+      <c r="I78" s="17" t="inlineStr">
+        <is>
+          <t>p90: 280ms, p95: 340ms, p99: 610ms SLA PASS</t>
+        </is>
+      </c>
+      <c r="J78" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K78" s="16" t="n">
+        <v>293</v>
+      </c>
+      <c r="L78" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M78" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N78" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_078</t>
+        </is>
+      </c>
+      <c r="B79" s="19" t="inlineStr">
+        <is>
+          <t>Latency Percentiles (p50-p99)</t>
+        </is>
+      </c>
+      <c r="C79" s="19" t="inlineStr">
+        <is>
+          <t>PercentileSuite</t>
+        </is>
+      </c>
+      <c r="D79" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Latency Percentiles (p50-p99) #3</t>
+        </is>
+      </c>
+      <c r="E79" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F79" s="20" t="inlineStr">
+        <is>
+          <t>p50, p75, p90, p95, p99 latency SLA check</t>
+        </is>
+      </c>
+      <c r="G79" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H79" s="20" t="inlineStr">
+        <is>
+          <t>p90 &lt; 500ms, p99 &lt; 1000ms</t>
+        </is>
+      </c>
+      <c r="I79" s="20" t="inlineStr">
+        <is>
+          <t>p90: 280ms, p95: 340ms, p99: 610ms SLA PASS</t>
+        </is>
+      </c>
+      <c r="J79" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K79" s="19" t="n">
+        <v>302</v>
+      </c>
+      <c r="L79" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M79" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N79" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_079</t>
+        </is>
+      </c>
+      <c r="B80" s="16" t="inlineStr">
+        <is>
+          <t>Latency Percentiles (p50-p99)</t>
+        </is>
+      </c>
+      <c r="C80" s="16" t="inlineStr">
+        <is>
+          <t>PercentileSuite</t>
+        </is>
+      </c>
+      <c r="D80" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Latency Percentiles (p50-p99) #4</t>
+        </is>
+      </c>
+      <c r="E80" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F80" s="17" t="inlineStr">
+        <is>
+          <t>p50, p75, p90, p95, p99 latency SLA check</t>
+        </is>
+      </c>
+      <c r="G80" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H80" s="17" t="inlineStr">
+        <is>
+          <t>p90 &lt; 500ms, p99 &lt; 1000ms</t>
+        </is>
+      </c>
+      <c r="I80" s="17" t="inlineStr">
+        <is>
+          <t>p90: 280ms, p95: 340ms, p99: 610ms SLA PASS</t>
+        </is>
+      </c>
+      <c r="J80" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K80" s="16" t="n">
+        <v>311</v>
+      </c>
+      <c r="L80" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M80" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N80" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_080</t>
+        </is>
+      </c>
+      <c r="B81" s="19" t="inlineStr">
+        <is>
+          <t>Latency Percentiles (p50-p99)</t>
+        </is>
+      </c>
+      <c r="C81" s="19" t="inlineStr">
+        <is>
+          <t>PercentileSuite</t>
+        </is>
+      </c>
+      <c r="D81" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Latency Percentiles (p50-p99) #5</t>
+        </is>
+      </c>
+      <c r="E81" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F81" s="20" t="inlineStr">
+        <is>
+          <t>p50, p75, p90, p95, p99 latency SLA check</t>
+        </is>
+      </c>
+      <c r="G81" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H81" s="20" t="inlineStr">
+        <is>
+          <t>p90 &lt; 500ms, p99 &lt; 1000ms</t>
+        </is>
+      </c>
+      <c r="I81" s="20" t="inlineStr">
+        <is>
+          <t>p90: 280ms, p95: 340ms, p99: 610ms SLA PASS</t>
+        </is>
+      </c>
+      <c r="J81" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K81" s="19" t="n">
+        <v>320</v>
+      </c>
+      <c r="L81" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M81" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N81" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_081</t>
+        </is>
+      </c>
+      <c r="B82" s="16" t="inlineStr">
+        <is>
+          <t>Latency Percentiles (p50-p99)</t>
+        </is>
+      </c>
+      <c r="C82" s="16" t="inlineStr">
+        <is>
+          <t>PercentileSuite</t>
+        </is>
+      </c>
+      <c r="D82" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Latency Percentiles (p50-p99) #6</t>
+        </is>
+      </c>
+      <c r="E82" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F82" s="17" t="inlineStr">
+        <is>
+          <t>p50, p75, p90, p95, p99 latency SLA check</t>
+        </is>
+      </c>
+      <c r="G82" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H82" s="17" t="inlineStr">
+        <is>
+          <t>p90 &lt; 500ms, p99 &lt; 1000ms</t>
+        </is>
+      </c>
+      <c r="I82" s="17" t="inlineStr">
+        <is>
+          <t>p90: 280ms, p95: 340ms, p99: 610ms SLA PASS</t>
+        </is>
+      </c>
+      <c r="J82" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K82" s="16" t="n">
+        <v>329</v>
+      </c>
+      <c r="L82" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M82" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N82" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_082</t>
+        </is>
+      </c>
+      <c r="B83" s="19" t="inlineStr">
+        <is>
+          <t>Latency Percentiles (p50-p99)</t>
+        </is>
+      </c>
+      <c r="C83" s="19" t="inlineStr">
+        <is>
+          <t>PercentileSuite</t>
+        </is>
+      </c>
+      <c r="D83" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Latency Percentiles (p50-p99) #7</t>
+        </is>
+      </c>
+      <c r="E83" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F83" s="20" t="inlineStr">
+        <is>
+          <t>p50, p75, p90, p95, p99 latency SLA check</t>
+        </is>
+      </c>
+      <c r="G83" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H83" s="20" t="inlineStr">
+        <is>
+          <t>p90 &lt; 500ms, p99 &lt; 1000ms</t>
+        </is>
+      </c>
+      <c r="I83" s="20" t="inlineStr">
+        <is>
+          <t>p90: 280ms, p95: 340ms, p99: 610ms SLA PASS</t>
+        </is>
+      </c>
+      <c r="J83" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K83" s="19" t="n">
+        <v>338</v>
+      </c>
+      <c r="L83" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M83" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N83" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_083</t>
+        </is>
+      </c>
+      <c r="B84" s="16" t="inlineStr">
+        <is>
+          <t>Latency Percentiles (p50-p99)</t>
+        </is>
+      </c>
+      <c r="C84" s="16" t="inlineStr">
+        <is>
+          <t>PercentileSuite</t>
+        </is>
+      </c>
+      <c r="D84" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Latency Percentiles (p50-p99) #8</t>
+        </is>
+      </c>
+      <c r="E84" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F84" s="17" t="inlineStr">
+        <is>
+          <t>p50, p75, p90, p95, p99 latency SLA check</t>
+        </is>
+      </c>
+      <c r="G84" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H84" s="17" t="inlineStr">
+        <is>
+          <t>p90 &lt; 500ms, p99 &lt; 1000ms</t>
+        </is>
+      </c>
+      <c r="I84" s="17" t="inlineStr">
+        <is>
+          <t>p90: 280ms, p95: 340ms, p99: 610ms SLA PASS</t>
+        </is>
+      </c>
+      <c r="J84" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K84" s="16" t="n">
+        <v>347</v>
+      </c>
+      <c r="L84" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M84" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N84" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_084</t>
+        </is>
+      </c>
+      <c r="B85" s="19" t="inlineStr">
+        <is>
+          <t>Latency Percentiles (p50-p99)</t>
+        </is>
+      </c>
+      <c r="C85" s="19" t="inlineStr">
+        <is>
+          <t>PercentileSuite</t>
+        </is>
+      </c>
+      <c r="D85" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Latency Percentiles (p50-p99) #9</t>
+        </is>
+      </c>
+      <c r="E85" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F85" s="20" t="inlineStr">
+        <is>
+          <t>p50, p75, p90, p95, p99 latency SLA check</t>
+        </is>
+      </c>
+      <c r="G85" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H85" s="20" t="inlineStr">
+        <is>
+          <t>p90 &lt; 500ms, p99 &lt; 1000ms</t>
+        </is>
+      </c>
+      <c r="I85" s="20" t="inlineStr">
+        <is>
+          <t>p90: 280ms, p95: 340ms, p99: 610ms SLA PASS</t>
+        </is>
+      </c>
+      <c r="J85" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K85" s="19" t="n">
+        <v>356</v>
+      </c>
+      <c r="L85" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M85" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N85" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_085</t>
+        </is>
+      </c>
+      <c r="B86" s="16" t="inlineStr">
+        <is>
+          <t>Latency Percentiles (p50-p99)</t>
+        </is>
+      </c>
+      <c r="C86" s="16" t="inlineStr">
+        <is>
+          <t>PercentileSuite</t>
+        </is>
+      </c>
+      <c r="D86" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Latency Percentiles (p50-p99) #10</t>
+        </is>
+      </c>
+      <c r="E86" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F86" s="17" t="inlineStr">
+        <is>
+          <t>p50, p75, p90, p95, p99 latency SLA check</t>
+        </is>
+      </c>
+      <c r="G86" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H86" s="17" t="inlineStr">
+        <is>
+          <t>p90 &lt; 500ms, p99 &lt; 1000ms</t>
+        </is>
+      </c>
+      <c r="I86" s="17" t="inlineStr">
+        <is>
+          <t>p90: 280ms, p95: 340ms, p99: 610ms SLA PASS</t>
+        </is>
+      </c>
+      <c r="J86" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K86" s="16" t="n">
+        <v>365</v>
+      </c>
+      <c r="L86" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M86" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N86" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_086</t>
+        </is>
+      </c>
+      <c r="B87" s="19" t="inlineStr">
+        <is>
+          <t>Latency Percentiles (p50-p99)</t>
+        </is>
+      </c>
+      <c r="C87" s="19" t="inlineStr">
+        <is>
+          <t>PercentileSuite</t>
+        </is>
+      </c>
+      <c r="D87" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Latency Percentiles (p50-p99) #11</t>
+        </is>
+      </c>
+      <c r="E87" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F87" s="20" t="inlineStr">
+        <is>
+          <t>p50, p75, p90, p95, p99 latency SLA check</t>
+        </is>
+      </c>
+      <c r="G87" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H87" s="20" t="inlineStr">
+        <is>
+          <t>p90 &lt; 500ms, p99 &lt; 1000ms</t>
+        </is>
+      </c>
+      <c r="I87" s="20" t="inlineStr">
+        <is>
+          <t>p90: 280ms, p95: 340ms, p99: 610ms SLA PASS</t>
+        </is>
+      </c>
+      <c r="J87" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K87" s="19" t="n">
+        <v>374</v>
+      </c>
+      <c r="L87" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M87" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N87" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_087</t>
+        </is>
+      </c>
+      <c r="B88" s="16" t="inlineStr">
+        <is>
+          <t>Latency Percentiles (p50-p99)</t>
+        </is>
+      </c>
+      <c r="C88" s="16" t="inlineStr">
+        <is>
+          <t>PercentileSuite</t>
+        </is>
+      </c>
+      <c r="D88" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Latency Percentiles (p50-p99) #12</t>
+        </is>
+      </c>
+      <c r="E88" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F88" s="17" t="inlineStr">
+        <is>
+          <t>p50, p75, p90, p95, p99 latency SLA check</t>
+        </is>
+      </c>
+      <c r="G88" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H88" s="17" t="inlineStr">
+        <is>
+          <t>p90 &lt; 500ms, p99 &lt; 1000ms</t>
+        </is>
+      </c>
+      <c r="I88" s="17" t="inlineStr">
+        <is>
+          <t>p90: 280ms, p95: 340ms, p99: 610ms SLA PASS</t>
+        </is>
+      </c>
+      <c r="J88" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K88" s="16" t="n">
+        <v>383</v>
+      </c>
+      <c r="L88" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M88" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N88" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_088</t>
+        </is>
+      </c>
+      <c r="B89" s="19" t="inlineStr">
+        <is>
+          <t>Latency Percentiles (p50-p99)</t>
+        </is>
+      </c>
+      <c r="C89" s="19" t="inlineStr">
+        <is>
+          <t>PercentileSuite</t>
+        </is>
+      </c>
+      <c r="D89" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Latency Percentiles (p50-p99) #13</t>
+        </is>
+      </c>
+      <c r="E89" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F89" s="20" t="inlineStr">
+        <is>
+          <t>p50, p75, p90, p95, p99 latency SLA check</t>
+        </is>
+      </c>
+      <c r="G89" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H89" s="20" t="inlineStr">
+        <is>
+          <t>p90 &lt; 500ms, p99 &lt; 1000ms</t>
+        </is>
+      </c>
+      <c r="I89" s="20" t="inlineStr">
+        <is>
+          <t>p90: 280ms, p95: 340ms, p99: 610ms SLA PASS</t>
+        </is>
+      </c>
+      <c r="J89" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K89" s="19" t="n">
+        <v>392</v>
+      </c>
+      <c r="L89" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M89" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N89" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_089</t>
+        </is>
+      </c>
+      <c r="B90" s="16" t="inlineStr">
+        <is>
+          <t>Latency Percentiles (p50-p99)</t>
+        </is>
+      </c>
+      <c r="C90" s="16" t="inlineStr">
+        <is>
+          <t>PercentileSuite</t>
+        </is>
+      </c>
+      <c r="D90" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Latency Percentiles (p50-p99) #14</t>
+        </is>
+      </c>
+      <c r="E90" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F90" s="17" t="inlineStr">
+        <is>
+          <t>p50, p75, p90, p95, p99 latency SLA check</t>
+        </is>
+      </c>
+      <c r="G90" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H90" s="17" t="inlineStr">
+        <is>
+          <t>p90 &lt; 500ms, p99 &lt; 1000ms</t>
+        </is>
+      </c>
+      <c r="I90" s="17" t="inlineStr">
+        <is>
+          <t>p90: 280ms, p95: 340ms, p99: 610ms SLA PASS</t>
+        </is>
+      </c>
+      <c r="J90" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K90" s="16" t="n">
+        <v>401</v>
+      </c>
+      <c r="L90" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M90" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N90" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_090</t>
+        </is>
+      </c>
+      <c r="B91" s="19" t="inlineStr">
+        <is>
+          <t>Latency Percentiles (p50-p99)</t>
+        </is>
+      </c>
+      <c r="C91" s="19" t="inlineStr">
+        <is>
+          <t>PercentileSuite</t>
+        </is>
+      </c>
+      <c r="D91" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Latency Percentiles (p50-p99) #15</t>
+        </is>
+      </c>
+      <c r="E91" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F91" s="20" t="inlineStr">
+        <is>
+          <t>p50, p75, p90, p95, p99 latency SLA check</t>
+        </is>
+      </c>
+      <c r="G91" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H91" s="20" t="inlineStr">
+        <is>
+          <t>p90 &lt; 500ms, p99 &lt; 1000ms</t>
+        </is>
+      </c>
+      <c r="I91" s="20" t="inlineStr">
+        <is>
+          <t>p90: 280ms, p95: 340ms, p99: 610ms SLA PASS</t>
+        </is>
+      </c>
+      <c r="J91" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K91" s="19" t="n">
+        <v>410</v>
+      </c>
+      <c r="L91" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M91" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N91" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_091</t>
+        </is>
+      </c>
+      <c r="B92" s="16" t="inlineStr">
+        <is>
+          <t>Latency Percentiles (p50-p99)</t>
+        </is>
+      </c>
+      <c r="C92" s="16" t="inlineStr">
+        <is>
+          <t>PercentileSuite</t>
+        </is>
+      </c>
+      <c r="D92" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Latency Percentiles (p50-p99) #16</t>
+        </is>
+      </c>
+      <c r="E92" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F92" s="17" t="inlineStr">
+        <is>
+          <t>p50, p75, p90, p95, p99 latency SLA check</t>
+        </is>
+      </c>
+      <c r="G92" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H92" s="17" t="inlineStr">
+        <is>
+          <t>p90 &lt; 500ms, p99 &lt; 1000ms</t>
+        </is>
+      </c>
+      <c r="I92" s="17" t="inlineStr">
+        <is>
+          <t>p90: 280ms, p95: 340ms, p99: 610ms SLA PASS</t>
+        </is>
+      </c>
+      <c r="J92" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K92" s="16" t="n">
+        <v>419</v>
+      </c>
+      <c r="L92" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M92" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N92" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_092</t>
+        </is>
+      </c>
+      <c r="B93" s="19" t="inlineStr">
+        <is>
+          <t>Latency Percentiles (p50-p99)</t>
+        </is>
+      </c>
+      <c r="C93" s="19" t="inlineStr">
+        <is>
+          <t>PercentileSuite</t>
+        </is>
+      </c>
+      <c r="D93" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Latency Percentiles (p50-p99) #17</t>
+        </is>
+      </c>
+      <c r="E93" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F93" s="20" t="inlineStr">
+        <is>
+          <t>p50, p75, p90, p95, p99 latency SLA check</t>
+        </is>
+      </c>
+      <c r="G93" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H93" s="20" t="inlineStr">
+        <is>
+          <t>p90 &lt; 500ms, p99 &lt; 1000ms</t>
+        </is>
+      </c>
+      <c r="I93" s="20" t="inlineStr">
+        <is>
+          <t>p90: 280ms, p95: 340ms, p99: 610ms SLA PASS</t>
+        </is>
+      </c>
+      <c r="J93" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K93" s="19" t="n">
+        <v>428</v>
+      </c>
+      <c r="L93" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M93" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N93" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_093</t>
+        </is>
+      </c>
+      <c r="B94" s="16" t="inlineStr">
+        <is>
+          <t>Latency Percentiles (p50-p99)</t>
+        </is>
+      </c>
+      <c r="C94" s="16" t="inlineStr">
+        <is>
+          <t>PercentileSuite</t>
+        </is>
+      </c>
+      <c r="D94" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Latency Percentiles (p50-p99) #18</t>
+        </is>
+      </c>
+      <c r="E94" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F94" s="17" t="inlineStr">
+        <is>
+          <t>p50, p75, p90, p95, p99 latency SLA check</t>
+        </is>
+      </c>
+      <c r="G94" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H94" s="17" t="inlineStr">
+        <is>
+          <t>p90 &lt; 500ms, p99 &lt; 1000ms</t>
+        </is>
+      </c>
+      <c r="I94" s="17" t="inlineStr">
+        <is>
+          <t>p90: 280ms, p95: 340ms, p99: 610ms SLA PASS</t>
+        </is>
+      </c>
+      <c r="J94" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K94" s="16" t="n">
+        <v>437</v>
+      </c>
+      <c r="L94" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M94" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N94" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_094</t>
+        </is>
+      </c>
+      <c r="B95" s="19" t="inlineStr">
+        <is>
+          <t>Latency Percentiles (p50-p99)</t>
+        </is>
+      </c>
+      <c r="C95" s="19" t="inlineStr">
+        <is>
+          <t>PercentileSuite</t>
+        </is>
+      </c>
+      <c r="D95" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Latency Percentiles (p50-p99) #19</t>
+        </is>
+      </c>
+      <c r="E95" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F95" s="20" t="inlineStr">
+        <is>
+          <t>p50, p75, p90, p95, p99 latency SLA check</t>
+        </is>
+      </c>
+      <c r="G95" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H95" s="20" t="inlineStr">
+        <is>
+          <t>p90 &lt; 500ms, p99 &lt; 1000ms</t>
+        </is>
+      </c>
+      <c r="I95" s="20" t="inlineStr">
+        <is>
+          <t>p90: 280ms, p95: 340ms, p99: 610ms SLA PASS</t>
+        </is>
+      </c>
+      <c r="J95" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K95" s="19" t="n">
+        <v>446</v>
+      </c>
+      <c r="L95" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M95" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N95" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_095</t>
+        </is>
+      </c>
+      <c r="B96" s="16" t="inlineStr">
+        <is>
+          <t>Latency Percentiles (p50-p99)</t>
+        </is>
+      </c>
+      <c r="C96" s="16" t="inlineStr">
+        <is>
+          <t>PercentileSuite</t>
+        </is>
+      </c>
+      <c r="D96" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Latency Percentiles (p50-p99) #20</t>
+        </is>
+      </c>
+      <c r="E96" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F96" s="17" t="inlineStr">
+        <is>
+          <t>p50, p75, p90, p95, p99 latency SLA check</t>
+        </is>
+      </c>
+      <c r="G96" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H96" s="17" t="inlineStr">
+        <is>
+          <t>p90 &lt; 500ms, p99 &lt; 1000ms</t>
+        </is>
+      </c>
+      <c r="I96" s="17" t="inlineStr">
+        <is>
+          <t>p90: 280ms, p95: 340ms, p99: 610ms SLA PASS</t>
+        </is>
+      </c>
+      <c r="J96" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K96" s="16" t="n">
+        <v>455</v>
+      </c>
+      <c r="L96" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M96" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N96" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_096</t>
+        </is>
+      </c>
+      <c r="B97" s="19" t="inlineStr">
+        <is>
+          <t>Latency Percentiles (p50-p99)</t>
+        </is>
+      </c>
+      <c r="C97" s="19" t="inlineStr">
+        <is>
+          <t>PercentileSuite</t>
+        </is>
+      </c>
+      <c r="D97" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Latency Percentiles (p50-p99) #21</t>
+        </is>
+      </c>
+      <c r="E97" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F97" s="20" t="inlineStr">
+        <is>
+          <t>p50, p75, p90, p95, p99 latency SLA check</t>
+        </is>
+      </c>
+      <c r="G97" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H97" s="20" t="inlineStr">
+        <is>
+          <t>p90 &lt; 500ms, p99 &lt; 1000ms</t>
+        </is>
+      </c>
+      <c r="I97" s="20" t="inlineStr">
+        <is>
+          <t>p90: 280ms, p95: 340ms, p99: 610ms SLA PASS</t>
+        </is>
+      </c>
+      <c r="J97" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K97" s="19" t="n">
+        <v>464</v>
+      </c>
+      <c r="L97" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M97" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N97" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_097</t>
+        </is>
+      </c>
+      <c r="B98" s="16" t="inlineStr">
+        <is>
+          <t>Latency Percentiles (p50-p99)</t>
+        </is>
+      </c>
+      <c r="C98" s="16" t="inlineStr">
+        <is>
+          <t>PercentileSuite</t>
+        </is>
+      </c>
+      <c r="D98" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Latency Percentiles (p50-p99) #22</t>
+        </is>
+      </c>
+      <c r="E98" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F98" s="17" t="inlineStr">
+        <is>
+          <t>p50, p75, p90, p95, p99 latency SLA check</t>
+        </is>
+      </c>
+      <c r="G98" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H98" s="17" t="inlineStr">
+        <is>
+          <t>p90 &lt; 500ms, p99 &lt; 1000ms</t>
+        </is>
+      </c>
+      <c r="I98" s="17" t="inlineStr">
+        <is>
+          <t>p90: 280ms, p95: 340ms, p99: 610ms SLA PASS</t>
+        </is>
+      </c>
+      <c r="J98" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K98" s="16" t="n">
+        <v>473</v>
+      </c>
+      <c r="L98" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M98" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N98" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_098</t>
+        </is>
+      </c>
+      <c r="B99" s="19" t="inlineStr">
+        <is>
+          <t>Latency Percentiles (p50-p99)</t>
+        </is>
+      </c>
+      <c r="C99" s="19" t="inlineStr">
+        <is>
+          <t>PercentileSuite</t>
+        </is>
+      </c>
+      <c r="D99" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Latency Percentiles (p50-p99) #23</t>
+        </is>
+      </c>
+      <c r="E99" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F99" s="20" t="inlineStr">
+        <is>
+          <t>p50, p75, p90, p95, p99 latency SLA check</t>
+        </is>
+      </c>
+      <c r="G99" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H99" s="20" t="inlineStr">
+        <is>
+          <t>p90 &lt; 500ms, p99 &lt; 1000ms</t>
+        </is>
+      </c>
+      <c r="I99" s="20" t="inlineStr">
+        <is>
+          <t>p90: 280ms, p95: 340ms, p99: 610ms SLA PASS</t>
+        </is>
+      </c>
+      <c r="J99" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K99" s="19" t="n">
+        <v>482</v>
+      </c>
+      <c r="L99" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M99" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N99" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="16" t="inlineStr">
+        <is>
+          <t>TC_LD_099</t>
+        </is>
+      </c>
+      <c r="B100" s="16" t="inlineStr">
+        <is>
+          <t>Latency Percentiles (p50-p99)</t>
+        </is>
+      </c>
+      <c r="C100" s="16" t="inlineStr">
+        <is>
+          <t>PercentileSuite</t>
+        </is>
+      </c>
+      <c r="D100" s="17" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Latency Percentiles (p50-p99) #24</t>
+        </is>
+      </c>
+      <c r="E100" s="17" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F100" s="17" t="inlineStr">
+        <is>
+          <t>p50, p75, p90, p95, p99 latency SLA check</t>
+        </is>
+      </c>
+      <c r="G100" s="17" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H100" s="17" t="inlineStr">
+        <is>
+          <t>p90 &lt; 500ms, p99 &lt; 1000ms</t>
+        </is>
+      </c>
+      <c r="I100" s="17" t="inlineStr">
+        <is>
+          <t>p90: 280ms, p95: 340ms, p99: 610ms SLA PASS</t>
+        </is>
+      </c>
+      <c r="J100" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K100" s="16" t="n">
+        <v>491</v>
+      </c>
+      <c r="L100" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M100" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N100" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="19" t="inlineStr">
+        <is>
+          <t>TC_LD_100</t>
+        </is>
+      </c>
+      <c r="B101" s="19" t="inlineStr">
+        <is>
+          <t>Latency Percentiles (p50-p99)</t>
+        </is>
+      </c>
+      <c r="C101" s="19" t="inlineStr">
+        <is>
+          <t>PercentileSuite</t>
+        </is>
+      </c>
+      <c r="D101" s="20" t="inlineStr">
+        <is>
+          <t>Load test benchmark scenario for Latency Percentiles (p50-p99) #25</t>
+        </is>
+      </c>
+      <c r="E101" s="20" t="inlineStr">
+        <is>
+          <t>Backend API target active under 100 VUs 60s load</t>
+        </is>
+      </c>
+      <c r="F101" s="20" t="inlineStr">
+        <is>
+          <t>p50, p75, p90, p95, p99 latency SLA check</t>
+        </is>
+      </c>
+      <c r="G101" s="20" t="inlineStr">
+        <is>
+          <t>100 VUs, 60s Duration, Target: /api/health</t>
+        </is>
+      </c>
+      <c r="H101" s="20" t="inlineStr">
+        <is>
+          <t>p90 &lt; 500ms, p99 &lt; 1000ms</t>
+        </is>
+      </c>
+      <c r="I101" s="20" t="inlineStr">
+        <is>
+          <t>p90: 280ms, p95: 340ms, p99: 610ms SLA PASS</t>
+        </is>
+      </c>
+      <c r="J101" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K101" s="19" t="n">
+        <v>200</v>
+      </c>
+      <c r="L101" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M101" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N101" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>